--- a/resources/qa_test/formula_samples/formula_sum.xlsx
+++ b/resources/qa_test/formula_samples/formula_sum.xlsx
@@ -1,39 +1,92 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="SeasonStat" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="SeasonStat"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>赛季编号</t>
+  </si>
+  <si>
+    <t>场次1</t>
+  </si>
+  <si>
+    <t>场次2</t>
+  </si>
+  <si>
+    <t>场次3</t>
+  </si>
+  <si>
+    <t>场次4</t>
+  </si>
+  <si>
+    <t>总场次</t>
+  </si>
+  <si>
+    <t>平均场次</t>
+  </si>
+  <si>
+    <t>最高单场</t>
+  </si>
+  <si>
+    <t>season_id:int</t>
+  </si>
+  <si>
+    <t>c1:int</t>
+  </si>
+  <si>
+    <t>c2:int</t>
+  </si>
+  <si>
+    <t>c3:int</t>
+  </si>
+  <si>
+    <t>c4:int</t>
+  </si>
+  <si>
+    <t>total:int</t>
+  </si>
+  <si>
+    <t>avg:float</t>
+  </si>
+  <si>
+    <t>max:int</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -56,107 +109,39 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="7">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -444,382 +429,353 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="6" max="6"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="7" max="7"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="6" min="8" max="8"/>
+    <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>赛季编号</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>场次1</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>场次2</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>场次3</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>场次4</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>总场次</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>平均场次</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>最高单场</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>season_id:int</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>c1:int</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>c2:int</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>c3:int</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>c4:int</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>total:int</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>avg:float</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>max:int</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="3" t="n">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3">
+        <v>15</v>
+      </c>
+      <c r="D3" s="3">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4">
+        <f>SUM(B3:E3)</f>
+      </c>
+      <c r="G3" s="4">
+        <f>AVERAGE(B3:E3)</f>
+      </c>
+      <c r="H3" s="4">
+        <f>MAX(B3:E3)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
         <v>20</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C4" s="3">
         <v>25</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D4" s="3">
         <v>23</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>999</v>
-      </c>
-      <c r="F3" s="8">
-        <f>SUM(B3:E3)</f>
-        <v/>
-      </c>
-      <c r="G3" s="8">
-        <f>AVERAGE(B3:E3)</f>
-        <v/>
-      </c>
-      <c r="H3" s="8">
-        <f>MAX(B3:E3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="3" t="n">
+      <c r="E4" s="3">
+        <v>28</v>
+      </c>
+      <c r="F4" s="4">
+        <f>SUM(B4:E4)</f>
+      </c>
+      <c r="G4" s="4">
+        <f>AVERAGE(B4:E4)</f>
+      </c>
+      <c r="H4" s="4">
+        <f>MAX(B4:E4)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3">
+        <v>33</v>
+      </c>
+      <c r="E5" s="3">
+        <v>38</v>
+      </c>
+      <c r="F5" s="4">
+        <f>SUM(B5:E5)</f>
+      </c>
+      <c r="G5" s="4">
+        <f>AVERAGE(B5:E5)</f>
+      </c>
+      <c r="H5" s="4">
+        <f>MAX(B5:E5)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B6" s="3">
         <v>40</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C6" s="3">
         <v>45</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D6" s="3">
         <v>43</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="F4" s="8">
-        <f>SUM(B4:E4)</f>
-        <v/>
-      </c>
-      <c r="G4" s="8">
-        <f>AVERAGE(B4:E4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="8">
-        <f>MAX(B4:E4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="3" t="n">
+      <c r="E6" s="3">
+        <v>48</v>
+      </c>
+      <c r="F6" s="4">
+        <f>SUM(B6:E6)</f>
+      </c>
+      <c r="G6" s="4">
+        <f>AVERAGE(B6:E6)</f>
+      </c>
+      <c r="H6" s="4">
+        <f>MAX(B6:E6)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="3">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B7" s="3">
         <v>70</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C7" s="3">
         <v>75</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D7" s="3">
         <v>73</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E7" s="3">
         <v>78</v>
       </c>
-      <c r="F5" s="8">
-        <f>SUM(B5:E5)</f>
-        <v/>
-      </c>
-      <c r="G5" s="8">
-        <f>AVERAGE(B5:E5)</f>
-        <v/>
-      </c>
-      <c r="H5" s="8">
-        <f>MAX(B5:E5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="3" t="n">
+      <c r="F7" s="4">
+        <f>SUM(B7:E7)</f>
+      </c>
+      <c r="G7" s="4">
+        <f>AVERAGE(B7:E7)</f>
+      </c>
+      <c r="H7" s="4">
+        <f>MAX(B7:E7)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="3">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B8" s="3">
         <v>80</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C8" s="3">
         <v>85</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D8" s="3">
         <v>83</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E8" s="3">
         <v>88</v>
       </c>
-      <c r="F6" s="8">
-        <f>SUM(B6:E6)</f>
-        <v/>
-      </c>
-      <c r="G6" s="8">
-        <f>AVERAGE(B6:E6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="8">
-        <f>MAX(B6:E6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="3" t="n">
+      <c r="F8" s="4">
+        <f>SUM(B8:E8)</f>
+      </c>
+      <c r="G8" s="4">
+        <f>AVERAGE(B8:E8)</f>
+      </c>
+      <c r="H8" s="4">
+        <f>MAX(B8:E8)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="3">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B9" s="3">
         <v>90</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C9" s="3">
         <v>95</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D9" s="3">
         <v>93</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E9" s="3">
         <v>98</v>
       </c>
-      <c r="F7" s="8">
-        <f>SUM(B7:E7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="8">
-        <f>AVERAGE(B7:E7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="8">
-        <f>MAX(B7:E7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="3" t="n">
+      <c r="F9" s="4">
+        <f>SUM(B9:E9)</f>
+      </c>
+      <c r="G9" s="4">
+        <f>AVERAGE(B9:E9)</f>
+      </c>
+      <c r="H9" s="4">
+        <f>MAX(B9:E9)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="3">
         <v>10</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B10" s="3">
         <v>100</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C10" s="3">
         <v>105</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D10" s="3">
         <v>103</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E10" s="3">
         <v>108</v>
       </c>
-      <c r="F8" s="8">
-        <f>SUM(B8:E8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="8">
-        <f>AVERAGE(B8:E8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="8">
-        <f>MAX(B8:E8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="3" t="n">
+      <c r="F10" s="4">
+        <f>SUM(B10:E10)</f>
+      </c>
+      <c r="G10" s="4">
+        <f>AVERAGE(B10:E10)</f>
+      </c>
+      <c r="H10" s="4">
+        <f>MAX(B10:E10)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="3">
         <v>11</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B11" s="3">
         <v>110</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C11" s="3">
         <v>115</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D11" s="3">
         <v>113</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E11" s="3">
         <v>118</v>
       </c>
-      <c r="F9" s="8">
-        <f>SUM(B9:E9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="8">
-        <f>AVERAGE(B9:E9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="8">
-        <f>MAX(B9:E9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="3" t="n">
+      <c r="F11" s="4">
+        <f>SUM(B11:E11)</f>
+      </c>
+      <c r="G11" s="4">
+        <f>AVERAGE(B11:E11)</f>
+      </c>
+      <c r="H11" s="4">
+        <f>MAX(B11:E11)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="3">
         <v>12</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B12" s="3">
         <v>120</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C12" s="3">
         <v>125</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D12" s="3">
         <v>123</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E12" s="3">
         <v>128</v>
       </c>
-      <c r="F10" s="8">
-        <f>SUM(B10:E10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="8">
-        <f>AVERAGE(B10:E10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="8">
-        <f>MAX(B10:E10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="3" t="n">
+      <c r="F12" s="4">
+        <f>SUM(B12:E12)</f>
+      </c>
+      <c r="G12" s="4">
+        <f>AVERAGE(B12:E12)</f>
+      </c>
+      <c r="H12" s="4">
+        <f>MAX(B12:E12)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="3">
         <v>99</v>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="8">
-        <f>SUM(F3:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="8">
-        <f>AVERAGE(F3:F10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="8">
-        <f>MAX(F3:F10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-    </row>
-    <row r="13" ht="18.75" customHeight="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="4">
+        <f>SUM(F3:F12)</f>
+      </c>
+      <c r="G13" s="4">
+        <f>AVERAGE(F3:F12)</f>
+      </c>
+      <c r="H13" s="4">
+        <f>MAX(F3:F12)</f>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
